--- a/Data Files/AcessoAllianznetProducao/AcessoAllianznetProducao.xlsx
+++ b/Data Files/AcessoAllianznetProducao/AcessoAllianznetProducao.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20373"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\nasvdir100\Profile_BR\be54955\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\AcessoAllianznetProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B51C4D-91C8-40F0-9CCC-0498246BFEDC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB06A9DA-B5AC-4B08-8015-79E601599A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20610" windowHeight="8790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AcessoAllianznetProducao" sheetId="2" r:id="rId1"/>
@@ -2853,7 +2853,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.28515625" style="5" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="74.85546875" style="3" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="94" style="3" customWidth="1" collapsed="1"/>
     <col min="3" max="3" width="147.42578125" style="8" customWidth="1" collapsed="1"/>
     <col min="4" max="16384" width="9.140625" style="3" collapsed="1"/>
   </cols>
@@ -49755,31 +49755,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>